--- a/xiuxian配置表/yunxing_params/z_ui_strings_zh.xlsx
+++ b/xiuxian配置表/yunxing_params/z_ui_strings_zh.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="z_ui_strings_zh" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_ui_strings_zh" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,826 +535,766 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hover:skill:power</t>
+          <t>hover:skill:tags</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>威力：{value}</t>
+          <t>标签：{value}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hover:skill:tags</t>
+          <t>hover:skill:effect_damage</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>标签：{value}</t>
+          <t>对{target}造成伤害 {value}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hover:skill:effect_damage</t>
+          <t>hover:skill:effect_heal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>对{target}造成伤害 {value}</t>
+          <t>为{target}恢复 {value} 生命</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hover:skill:effect_heal</t>
+          <t>hover:skill:effect_shield</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>为{target}恢复 {value} 生命</t>
+          <t>为{target}获得护盾 {value}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hover:skill:effect_shield</t>
+          <t>hover:skill:effect_buff</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>为{target}获得护盾 {value}</t>
+          <t>对{target}施加 {name}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hover:skill:effect_buff</t>
+          <t>hover:skill:effect_buff_plain</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>对{target}施加 {name}</t>
+          <t>对{target}施加状态</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hover:skill:effect_buff_plain</t>
+          <t>hover:skill:tag:attack</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>对{target}施加状态</t>
+          <t>攻击</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hover:skill:tag:attack</t>
+          <t>hover:skill:tag:physical</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>物理</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hover:skill:tag:physical</t>
+          <t>hover:skill:tag:magic</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>物理</t>
+          <t>法术</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hover:skill:tag:magic</t>
+          <t>hover:skill:tag:fire</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>法术</t>
+          <t>火系</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hover:skill:tag:fire</t>
+          <t>hover:skill:tag:lightning</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>火系</t>
+          <t>雷系</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hover:skill:tag:lightning</t>
+          <t>hover:skill:tag:ice</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>雷系</t>
+          <t>冰系</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hover:skill:tag:ice</t>
+          <t>hover:skill:tag:shield</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>冰系</t>
+          <t>护盾</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hover:skill:tag:shield</t>
+          <t>hover:skill:tag:control</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>护盾</t>
+          <t>控制</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hover:skill:tag:control</t>
+          <t>hover:skill:tag:poison</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>控制</t>
+          <t>毒</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hover:skill:tag:poison</t>
+          <t>hover:item:count</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>毒</t>
+          <t>数量：{value}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hover:item:count</t>
+          <t>hover:item:effect_restore_mp</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>数量：{value}</t>
+          <t>为{target}恢复 {value} 法力</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hover:item:effect_restore_mp</t>
+          <t>hover:equip:kind</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>为{target}恢复 {value} 法力</t>
+          <t>战斗法宝</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hover:equip:kind</t>
+          <t>hover:buff:duration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>战斗法宝</t>
+          <t>持续：{value}秒</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hover:buff:stacks</t>
+          <t>hover:buff:max_stacks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>层数：{value}</t>
+          <t>最大层数：{value}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hover:buff:duration</t>
+          <t>hover:buff:ticktime</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>持续：{value}秒</t>
+          <t>周期：{value}秒</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hover:buff:max_stacks</t>
+          <t>hover:buff:modifier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>最大层数：{value}</t>
+          <t>{name} {sign}{value}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hover:buff:ticktime</t>
+          <t>hover:buff:tags</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周期：{value}秒</t>
+          <t>标签：{value}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hover:buff:modifier</t>
+          <t>hover:buff:tag:buff</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{name} {sign}{value}</t>
+          <t>增益</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hover:buff:tags</t>
+          <t>hover:buff:tag:debuff</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>标签：{value}</t>
+          <t>减益</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hover:buff:tag:buff</t>
+          <t>hover:buff:attr:hp_max</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>增益</t>
+          <t>气血上限</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hover:buff:tag:debuff</t>
+          <t>hover:buff:attr:mp_max</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>减益</t>
+          <t>法力上限</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hover:buff:attr:hp_max</t>
+          <t>hover:buff:attr:shield</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>气血上限</t>
+          <t>护盾</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hover:buff:attr:mp_max</t>
+          <t>hover:buff:attr:atk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>法力上限</t>
+          <t>攻击</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hover:buff:attr:shield</t>
+          <t>hover:buff:attr:def</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>护盾</t>
+          <t>防御</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hover:buff:attr:atk</t>
+          <t>hover:buff:attr:spd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>速度</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hover:buff:attr:def</t>
+          <t>item_info:type</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>类型：{value}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hover:buff:attr:spd</t>
+          <t>item_info:type_equip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>速度</t>
+          <t>法宝</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>item_info:type</t>
+          <t>item_info:quality</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>类型：{value}</t>
+          <t>品质：{value}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>item_info:type_equip</t>
+          <t>item_info:count</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>法宝</t>
+          <t>数量：{value}</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>item_info:quality</t>
+          <t>item_info:price</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>品质：{value}</t>
+          <t>灵石估价：{value}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>item_info:count</t>
+          <t>item_info:stack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>数量：{value}</t>
+          <t>可堆叠（上限 {value}）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>item_info:price</t>
+          <t>item_info:equip_kind</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>灵石估价：{value}</t>
+          <t>战斗法宝</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>item_info:stack</t>
+          <t>item_info:use_hp</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>可堆叠（上限 {value}）</t>
+          <t>使用效果：恢复气血 {value}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>item_info:equip_kind</t>
+          <t>item_info:use_mp</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>战斗法宝</t>
+          <t>使用效果：恢复法力 {value}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>item_info:use_hp</t>
+          <t>item_info:use_heart_demon</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>使用效果：恢复气血 {value}</t>
+          <t>使用效果：心魔 {value}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>item_info:use_mp</t>
+          <t>item_info:use_cultivation</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>使用效果：恢复法力 {value}</t>
+          <t>使用效果：修为 +{value}</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>item_info:use_heart_demon</t>
+          <t>item_info:use_instability</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>使用效果：心魔 {value}</t>
+          <t>使用效果：灵力驳杂 {value}</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>item_info:use_cultivation</t>
+          <t>item_info:use_pill_cultivation</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>使用效果：修为 +{value}</t>
+          <t>使用效果：修炼「丹药炼化」修为 +{value}</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>item_info:use_instability</t>
+          <t>item_info:use_injury</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>使用效果：灵力驳杂 {value}</t>
+          <t>使用效果：缩短伤势 {value} 日</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>item_info:use_pill_cultivation</t>
+          <t>item_info:use_sell_only</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>使用效果：修炼「丹药炼化」修为 +{value}</t>
+          <t>使用效果：无药效，仅可出售</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>item_info:use_injury</t>
+          <t>item_info:use_alchemy_mastery</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>使用效果：缩短伤势 {value} 日</t>
+          <t>使用效果：{recipe} 熟练度 +{value}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>item_info:use_sell_only</t>
+          <t>item_info:use_fight_prefix</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>使用效果：无药效，仅可出售</t>
+          <t>战斗使用：{value}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>item_info:use_alchemy_mastery</t>
+          <t>item_info:fight_mp_cost</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>使用效果：{recipe} 熟练度 +{value}</t>
+          <t>战斗消耗：法力 {value}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>item_info:use_fight_prefix</t>
+          <t>item_info:fight_cd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>战斗使用：{value}</t>
+          <t>战斗冷却：{value} 秒</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>item_info:fight_mp_cost</t>
+          <t>item_info:learn_ability</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>战斗消耗：法力 {value}</t>
+          <t>研读习得：技能 {value}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>item_info:fight_cd</t>
+          <t>item_info:learn_method</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>战斗冷却：{value} 秒</t>
+          <t>研读习得：功法 {value}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>item_info:learn_ability</t>
+          <t>item_info:learn_req_header</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>研读习得：技能 {value}</t>
+          <t>学习条件：</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>item_info:learn_method</t>
+          <t>item_info:learn_req_realm</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>研读习得：功法 {value}</t>
+          <t>境界要求：{need}（当前：{current}）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>item_info:learn_req_header</t>
+          <t>item_info:learn_req_knowledge</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>学习条件：</t>
+          <t>知识要求：{name} ≥ {need} 级（当前 {current} 级）</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>item_info:learn_req_realm</t>
+          <t>item_info:learn_hub_hint</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>境界要求：{need}（当前：{current}）</t>
+          <t>在洞府底部「研读」使用</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>item_info:learn_req_knowledge</t>
+          <t>item_info:use_study</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>知识要求：{name} ≥ {need} 级（当前 {current} 级）</t>
+          <t>研读</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>item_info:learn_hub_hint</t>
+          <t>combat:float:tiaoxi</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>在洞府底部「研读」使用</t>
+          <t>调息</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>item_info:use_study</t>
+          <t>combat:float:damage</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>研读</t>
+          <t>-{value}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>combat:float:tiaoxi</t>
+          <t>combat:float:heal</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>调息</t>
+          <t>+{value}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>combat:float:basic_attack</t>
+          <t>combat:float:mp_gain</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>调息</t>
+          <t>+{value} MP</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>combat:float:damage</t>
+          <t>combat:float:shield_absorb</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>-{value}</t>
+          <t>吸收</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>combat:float:heal</t>
+          <t>combat:float:buff_expire</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>+{value}</t>
+          <t>{name} 消散</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>combat:float:mp_cost</t>
+          <t>combat:float:buff_tick</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
-        <is>
-          <t>-{value} MP</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>combat:float:mp_gain</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>+{value} MP</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>combat:float:shield</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>盾 -{value}</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>combat:float:shield_absorb</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>吸收</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>combat:float:buff_expire</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>{name} 消散</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>combat:float:buff_tick</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -1405,7 +1345,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
